--- a/formatted_buildings.xlsx
+++ b/formatted_buildings.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Business\TOCOnnect\Code\Python Practice\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37553E0D-90CC-4EFD-B359-804E50664026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
   <si>
     <t>Address</t>
   </si>
@@ -73,29 +92,68 @@
     <t>Gross Rent</t>
   </si>
   <si>
-    <t xml:space="preserve">55 University Avenue </t>
-  </si>
-  <si>
-    <t xml:space="preserve">155 University Avenue </t>
-  </si>
-  <si>
-    <t>Downtown Toronto</t>
-  </si>
-  <si>
-    <t>Financial Core</t>
-  </si>
-  <si>
-    <t>Class A</t>
-  </si>
-  <si>
-    <t>Class B</t>
+    <t>Property_ID</t>
+  </si>
+  <si>
+    <t>1100 Burloak Dr</t>
+  </si>
+  <si>
+    <t>5420 N Service Rd</t>
+  </si>
+  <si>
+    <t>3390 S Service Rd</t>
+  </si>
+  <si>
+    <t>3215 N Service Rd</t>
+  </si>
+  <si>
+    <t>3310-3320 S Service Rd</t>
+  </si>
+  <si>
+    <t>Burlington</t>
+  </si>
+  <si>
+    <t>Oakville/Burlington</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>1550 Appleby Line</t>
+  </si>
+  <si>
+    <t>1450 Appleby Line</t>
+  </si>
+  <si>
+    <t>$14.50 - 15.50</t>
+  </si>
+  <si>
+    <t>$15.00 - 18.00</t>
+  </si>
+  <si>
+    <t>$17.75</t>
+  </si>
+  <si>
+    <t>$26.00</t>
+  </si>
+  <si>
+    <t>$15.95</t>
+  </si>
+  <si>
+    <t>$12.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,24 +205,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +279,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,6 +313,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,9 +348,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,11 +524,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="12" max="12" width="7.08984375" customWidth="1"/>
+    <col min="13" max="13" width="10.90625" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,104 +604,326 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2">
-        <v>264183</v>
-      </c>
-      <c r="F2">
-        <v>252442</v>
-      </c>
-      <c r="G2">
-        <v>18</v>
-      </c>
-      <c r="H2">
-        <v>14453</v>
-      </c>
-      <c r="I2">
-        <v>338</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2">
-        <v>1978</v>
-      </c>
-      <c r="L2">
-        <v>2500</v>
-      </c>
-      <c r="O2">
-        <v>22309</v>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4">
+        <v>112711</v>
+      </c>
+      <c r="G2" s="5">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6">
+        <v>56356</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="8">
+        <v>2001</v>
+      </c>
+      <c r="O2" s="9">
+        <v>93947</v>
       </c>
       <c r="P2">
-        <v>0.08444525196549361</v>
-      </c>
-      <c r="Q2">
-        <v>42144</v>
+        <f>O2/E2</f>
+        <v>0.83352112925978827</v>
+      </c>
+      <c r="Q2" s="10">
+        <v>93947</v>
       </c>
       <c r="R2">
-        <v>0.1595257832638739</v>
-      </c>
-      <c r="T2">
-        <v>29.24</v>
+        <f>Q2/E2</f>
+        <v>0.83352112925978827</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="10">
+        <v>112711</v>
+      </c>
+      <c r="G3" s="11">
+        <v>2</v>
+      </c>
+      <c r="H3" s="10">
+        <v>56356</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="11">
+        <v>2001</v>
+      </c>
+      <c r="O3" s="10">
+        <v>93947</v>
+      </c>
+      <c r="P3" s="10">
+        <f>O3/E3</f>
+        <v>0.83352112925978827</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>93947</v>
+      </c>
+      <c r="R3" s="10">
+        <f>Q3/E3</f>
+        <v>0.83352112925978827</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4">
+        <v>123875</v>
+      </c>
+      <c r="G4" s="5">
+        <v>7</v>
+      </c>
+      <c r="H4" s="6">
+        <v>17696</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1991</v>
+      </c>
+      <c r="O4" s="9">
+        <v>25019</v>
+      </c>
+      <c r="P4" s="10">
+        <f t="shared" ref="P4:P8" si="0">O4/E4</f>
+        <v>0.20196972754793138</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>43348</v>
+      </c>
+      <c r="R4" s="10">
+        <f t="shared" ref="R4:R8" si="1">Q4/E4</f>
+        <v>0.34993340060544903</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4">
+        <v>137796</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="6">
+        <v>23060</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1993</v>
+      </c>
+      <c r="O5" s="9">
+        <v>55397</v>
+      </c>
+      <c r="P5" s="10">
+        <f t="shared" si="0"/>
+        <v>0.40202182937095415</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>55397</v>
+      </c>
+      <c r="R5" s="10">
+        <f t="shared" si="1"/>
+        <v>0.40202182937095415</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3">
-        <v>178696</v>
-      </c>
-      <c r="F3">
-        <v>175696</v>
-      </c>
-      <c r="G3">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>10390</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4">
+        <v>61697</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6">
+        <v>18100</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1980</v>
+      </c>
+      <c r="O6" s="9">
+        <v>28447</v>
+      </c>
+      <c r="P6" s="10">
+        <f t="shared" si="0"/>
+        <v>0.46107590320436975</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>28447</v>
+      </c>
+      <c r="R6" s="10">
+        <f t="shared" si="1"/>
+        <v>0.46107590320436975</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20255</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="6">
+        <v>10128</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1966</v>
+      </c>
+      <c r="O7" s="9">
+        <v>16002</v>
+      </c>
+      <c r="P7" s="10">
+        <f t="shared" si="0"/>
+        <v>0.79002715378918786</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>16002</v>
+      </c>
+      <c r="R7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.79002715378918786</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3">
-        <v>1968</v>
-      </c>
-      <c r="O3">
-        <v>17190</v>
-      </c>
-      <c r="P3">
-        <v>0.09619689304741012</v>
-      </c>
-      <c r="Q3">
-        <v>27584</v>
-      </c>
-      <c r="R3">
-        <v>0.1543627165689215</v>
-      </c>
-      <c r="T3">
-        <v>27.74</v>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4">
+        <v>77435</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25811</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1986</v>
+      </c>
+      <c r="O8" s="9">
+        <v>39392</v>
+      </c>
+      <c r="P8" s="10">
+        <f t="shared" si="0"/>
+        <v>0.50871053141344358</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>39392</v>
+      </c>
+      <c r="R8" s="10">
+        <f t="shared" si="1"/>
+        <v>0.50871053141344358</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
